--- a/codex_tasks/艾尔登法环_第1至10大陆_NPC与经济框架_20260902/十大陆NPC与配方总账_V1.0.xlsx
+++ b/codex_tasks/艾尔登法环_第1至10大陆_NPC与经济框架_20260902/十大陆NPC与配方总账_V1.0.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使用说明" sheetId="1" r:id="Rce4e14fa26f145e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_NPC总览" sheetId="2" r:id="Rab6c4cbbf4aa4e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_配方总表" sheetId="3" r:id="R6b08532209fc415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_材料角色" sheetId="4" r:id="R5c1221c5954541cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_大陆经济口径" sheetId="5" r:id="R3706e2427d984920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_生肖与群攻" sheetId="6" r:id="R95f21e2a1b7541f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_属性来源" sheetId="7" r:id="R66b02746ca274834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_玩家模型" sheetId="8" r:id="Rb073cee81c904b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_校验" sheetId="9" r:id="R753eebfc89694c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使用说明" sheetId="1" r:id="R3dbb053c370a417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_NPC总览" sheetId="2" r:id="Rb7e8c9df2ba749a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_配方总表" sheetId="3" r:id="Re6f5124b9b5b4c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_材料角色" sheetId="4" r:id="R3c62d1dfbe604eea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_大陆经济口径" sheetId="5" r:id="Rdbcb077b7bd34688"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_生肖与群攻" sheetId="6" r:id="R1ab8f38cdb5f486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_属性来源" sheetId="7" r:id="R742ca3756d2e41ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_玩家模型" sheetId="8" r:id="Rb1bacb14d7a742ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_校验" sheetId="9" r:id="Rcec3256307e6450d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -858,7 +858,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d11549f0d54fe5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb630fb87706d4dd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2792,7 +2792,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4425f90b449c4574"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R146ad2cd07284b57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7424,7 +7424,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refdc57a3a7fe4547"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8541879a941146a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10932,7 +10932,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd33511bc15af4325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04cbabe755e2492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11456,7 +11456,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd90ded9429ba48d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7eafc1470d443bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12074,7 +12074,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdef7b882353f4ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e62f68a34824fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12375,7 +12375,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f9a53fa2527499d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12a61ac3fe494417"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12561,7 +12561,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd44b57fb934923"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e6da16ceb2d4f14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12918,7 +12918,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfebe113f8891414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R034a7fe048064c5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>